--- a/src/test/resources/TestData/TestData.xlsx
+++ b/src/test/resources/TestData/TestData.xlsx
@@ -19,13 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>PhoneNumber</t>
   </si>
@@ -73,9 +67,6 @@
   </si>
   <si>
     <t>ashwinimca96@gmail.com</t>
-  </si>
-  <si>
-    <t>RIS@2025</t>
   </si>
   <si>
     <t>Tenant</t>
@@ -957,27 +948,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1023,123 +1012,105 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>9954654734</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
         <v>16</v>
       </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>2500</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2">
+        <v>15</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>9954654734</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>9986794599</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3">
+        <v>13000</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3">
         <v>20</v>
       </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="N3" t="s">
         <v>22</v>
       </c>
-      <c r="J2">
-        <v>2500</v>
-      </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2">
-        <v>15</v>
-      </c>
-      <c r="P2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3">
-        <v>9986794599</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="O3" t="s">
         <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3">
-        <v>13000</v>
-      </c>
-      <c r="K3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3">
-        <v>20</v>
-      </c>
-      <c r="P3" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1"/>
-    <hyperlink ref="D3" r:id="rId2"/>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="B3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
